--- a/drybeans/data_final/acres_farms_county.xlsx
+++ b/drybeans/data_final/acres_farms_county.xlsx
@@ -40,16 +40,16 @@
     <t xml:space="preserve">GCFI $1 million or more</t>
   </si>
   <si>
+    <t xml:space="preserve">Not MWBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCFI less than $1 million</t>
+  </si>
+  <si>
     <t xml:space="preserve">MWBE</t>
   </si>
   <si>
-    <t xml:space="preserve">Not MWBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCFI less than $1 million</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soybeans</t>
+    <t xml:space="preserve">soybeans_only</t>
   </si>
   <si>
     <t xml:space="preserve">fips</t>
@@ -760,13 +760,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>371</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>3753</v>
+        <v>611</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0988542499333866</v>
+        <v>0.0425531914893617</v>
       </c>
     </row>
     <row r="3">
@@ -774,19 +774,19 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>1440</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>3753</v>
+        <v>611</v>
       </c>
       <c r="F3" t="n">
-        <v>0.383693045563549</v>
+        <v>0.0540098199672668</v>
       </c>
     </row>
     <row r="4">
@@ -794,39 +794,39 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>522</v>
+        <v>73</v>
       </c>
       <c r="E4" t="n">
-        <v>3753</v>
+        <v>611</v>
       </c>
       <c r="F4" t="n">
-        <v>0.139088729016787</v>
+        <v>0.119476268412439</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>1420</v>
+        <v>121</v>
       </c>
       <c r="E5" t="n">
-        <v>3753</v>
+        <v>37825</v>
       </c>
       <c r="F5" t="n">
-        <v>0.378363975486278</v>
+        <v>0.00319894249834765</v>
       </c>
     </row>
     <row r="6">
@@ -840,13 +840,13 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>9846</v>
+        <v>495</v>
       </c>
       <c r="E6" t="n">
-        <v>269793</v>
+        <v>37825</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0364946458951863</v>
+        <v>0.0130865829477859</v>
       </c>
     </row>
     <row r="7">
@@ -854,19 +854,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>40445</v>
+        <v>1817</v>
       </c>
       <c r="E7" t="n">
-        <v>269793</v>
+        <v>37825</v>
       </c>
       <c r="F7" t="n">
-        <v>0.149911228237945</v>
+        <v>0.0480370125578321</v>
       </c>
     </row>
     <row r="8">
@@ -874,39 +874,1279 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>53166</v>
+        <v>6094</v>
       </c>
       <c r="E8" t="n">
-        <v>269793</v>
+        <v>37825</v>
       </c>
       <c r="F8" t="n">
-        <v>0.197062192125074</v>
+        <v>0.161110376734964</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>166336</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>269793</v>
+        <v>611</v>
       </c>
       <c r="F9" t="n">
-        <v>0.616531933741795</v>
+        <v>0.0229132569558101</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>611</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.00981996726677578</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" t="n">
+        <v>611</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0212765957446809</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24</v>
+      </c>
+      <c r="E12" t="n">
+        <v>611</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0392798690671031</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>611</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0180032733224223</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>611</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0196399345335516</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>611</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0114566284779051</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>611</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0147299509001637</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16</v>
+      </c>
+      <c r="E17" t="n">
+        <v>611</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0261865793780687</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>611</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.00981996726677578</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" t="n">
+        <v>611</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0245499181669394</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" t="n">
+        <v>611</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0196399345335516</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="n">
+        <v>27</v>
+      </c>
+      <c r="E21" t="n">
+        <v>611</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.044189852700491</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" t="n">
+        <v>611</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0327332242225859</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>24</v>
+      </c>
+      <c r="E23" t="n">
+        <v>611</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0392798690671031</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>31</v>
+      </c>
+      <c r="E24" t="n">
+        <v>611</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0507364975450082</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" t="n">
+        <v>611</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0229132569558101</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>30</v>
+      </c>
+      <c r="E26" t="n">
+        <v>611</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.0490998363338789</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>40</v>
+      </c>
+      <c r="E27" t="n">
+        <v>611</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0654664484451719</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>39</v>
+      </c>
+      <c r="E28" t="n">
+        <v>611</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0638297872340425</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>51</v>
+      </c>
+      <c r="E29" t="n">
+        <v>611</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.0834697217675941</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>24</v>
+      </c>
+      <c r="E30" t="n">
+        <v>611</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0392798690671031</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>34</v>
+      </c>
+      <c r="E31" t="n">
+        <v>611</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0556464811783961</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="n">
+        <v>22</v>
+      </c>
+      <c r="E32" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.000581625908790482</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" t="n">
+        <v>21</v>
+      </c>
+      <c r="E33" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.000555188367481824</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.000211500330469266</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" t="n">
+        <v>92</v>
+      </c>
+      <c r="E35" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.00243225380039656</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="n">
+        <v>65</v>
+      </c>
+      <c r="E36" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.00171844018506279</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" t="n">
+        <v>48</v>
+      </c>
+      <c r="E37" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.0012690019828156</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15</v>
+      </c>
+      <c r="E38" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.000396563119629874</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" t="n">
+        <v>63</v>
+      </c>
+      <c r="E39" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.00166556510244547</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" t="n">
+        <v>20</v>
+      </c>
+      <c r="E40" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.000528750826173166</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" t="n">
+        <v>100</v>
+      </c>
+      <c r="E41" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.00264375413086583</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>88</v>
+      </c>
+      <c r="E42" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.00232650363516193</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" t="n">
+        <v>94</v>
+      </c>
+      <c r="E43" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.00248512888301388</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>28</v>
+      </c>
+      <c r="E44" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.000740251156642432</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>386</v>
+      </c>
+      <c r="E45" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.0102048909451421</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>308</v>
+      </c>
+      <c r="E46" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.00814276272306676</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" t="n">
+        <v>197</v>
+      </c>
+      <c r="E47" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.00520819563780568</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>59</v>
+      </c>
+      <c r="E48" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.00155981493721084</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" t="n">
+        <v>210</v>
+      </c>
+      <c r="E49" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.00555188367481824</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" t="n">
+        <v>93</v>
+      </c>
+      <c r="E50" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.00245869134170522</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" t="n">
+        <v>421</v>
+      </c>
+      <c r="E51" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.0111302048909451</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" t="n">
+        <v>367</v>
+      </c>
+      <c r="E52" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.00970257766027759</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" t="n">
+        <v>636</v>
+      </c>
+      <c r="E53" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.0168142762723067</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" t="n">
+        <v>105</v>
+      </c>
+      <c r="E54" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.00277594183740912</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1280</v>
+      </c>
+      <c r="E55" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.0338400528750826</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" t="n">
+        <v>546</v>
+      </c>
+      <c r="E56" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.0144348975545274</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" t="n">
+        <v>638</v>
+      </c>
+      <c r="E57" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.016867151354924</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" t="n">
+        <v>89</v>
+      </c>
+      <c r="E58" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.00235294117647059</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1342</v>
+      </c>
+      <c r="E59" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0354791804362194</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" t="n">
+        <v>363</v>
+      </c>
+      <c r="E60" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.00959682749504296</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1078</v>
+      </c>
+      <c r="E61" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.0284996695307336</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1168</v>
+      </c>
+      <c r="E62" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.0308790482485129</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1578</v>
+      </c>
+      <c r="E63" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.0417184401850628</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" t="n">
+        <v>221</v>
+      </c>
+      <c r="E64" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.00584269662921348</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4279</v>
+      </c>
+      <c r="E65" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.113126239259749</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2313</v>
+      </c>
+      <c r="E66" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.0611500330469266</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" t="s">
+        <v>9</v>
+      </c>
+      <c r="C67" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E67" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.0527164573694646</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" t="n">
+        <v>325</v>
+      </c>
+      <c r="E68" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.00859220092531395</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4061</v>
+      </c>
+      <c r="E69" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.107362855254461</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" t="n">
+        <v>710</v>
+      </c>
+      <c r="E70" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.0187706543291474</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C71" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3867</v>
+      </c>
+      <c r="E71" t="n">
+        <v>37825</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.102233972240582</v>
       </c>
     </row>
   </sheetData>
